--- a/app1/Excelfiles/March2024_15000.xlsx
+++ b/app1/Excelfiles/March2024_15000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -1180,13 +1180,43 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
         <v>17</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="F53" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="F54" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="F55" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="F56" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="F57" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
